--- a/data/output/evaluasi_34.xlsx
+++ b/data/output/evaluasi_34.xlsx
@@ -9,8 +9,10 @@
   <sheets>
     <sheet name="3400" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="3403" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3471" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3404" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3402" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3471" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3401" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +480,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2409.628974839658</v>
+        <v>-2409.629266811394</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -487,7 +489,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -506,7 +508,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>149.5350666940406</v>
+        <v>133.7627854764957</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -515,7 +517,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -530,20 +532,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.624342342519856</v>
+        <v>-98.68066324852232</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -558,20 +560,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-348.451967136502</v>
+        <v>9.162985647581685</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -586,20 +588,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1077.028809235933</v>
+        <v>8.265960976868923</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhk_pi_q2-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -618,16 +620,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-15.13918590075692</v>
+        <v>-348.4519671365023</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhk_pi_q1-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -646,16 +648,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-41.2884868851396</v>
+        <v>800.0169591160231</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhk_pi_q2-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -670,20 +672,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05705665057248134</v>
+        <v>-98.92145381229793</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25 vs distribusi_pi_q1-25.1</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -698,20 +700,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8010926819617318</v>
+        <v>-14.59281428745874</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>distribusi_pi_q2-25 vs distribusi_pi_q2-25.1</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -726,20 +728,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1325252353405573</v>
+        <v>-41.90178249712766</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -754,20 +756,496 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-24.79278327541278</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>34</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
+        <v>1.74091402536412</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q2-25 vs q-to-q_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.244157158360895</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>34</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.603819526811022</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>34</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-7.428144760762883</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>34</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.639106854505202</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>34</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6.663977429630795</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>34</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5.495947021478322</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>34</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8128496815725185</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>34</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9805094329584787</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>6.988885825573147</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>34</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.065976595014292</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>34</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6.988885825573147</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>34</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>7.610923472547286</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>34</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1581372970939969</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>34</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.264377873732973</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25 vs implisit_q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>34</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>0.8790490074489963</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>34</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Di Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3.270659091739277</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -782,7 +1260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,7 +1310,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-477492.87387378</v>
+        <v>3398261.09816449</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -841,7 +1319,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -856,20 +1334,300 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3422051.61440205</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q2-25_ril vs adhb_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1.372308852192716</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+      <c r="D4" t="n">
+        <v>2405468.661676627</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2384564.59047756</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q2-25_ril vs adhk_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>45.90997291244776</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>distribusi_net_ekspor_q1-25_ril vs distribusi_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>47.25311253566154</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>distribusi_net_ekspor_q2-25_ril vs distribusi_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.698776422094118</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.163938896769074</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.307021971725254</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1884339920647695</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8645427831130204</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1831326483856209</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -884,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,11 +1679,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3471</v>
+        <v>3404</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Yogyakarta</t>
+          <t>Kabupaten Sleman</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -934,26 +1692,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-235935.6200000001</v>
+        <v>-2.516995413711999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3471</v>
+        <v>3404</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Yogyakarta</t>
+          <t>Kabupaten Sleman</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -962,100 +1720,128 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.9623397717958523</v>
+        <v>-4.975137683225071</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3471</v>
+        <v>3404</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Yogyakarta</t>
+          <t>Kabupaten Sleman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.9623397717958523</v>
+        <v>-5.342837269020791</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3471</v>
+        <v>3404</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kota Yogyakarta</t>
+          <t>Kabupaten Sleman</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.06608063920303364</v>
+        <v>26.48501887104885</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3471</v>
+        <v>3404</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kota Yogyakarta</t>
+          <t>Kabupaten Sleman</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.134423193934054</v>
+        <v>22.96286614416383</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3404</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sleman</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.92728991666584</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,20 +1902,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.2617820599634658</v>
+        <v>4.012208605605512</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1144,20 +1930,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.2617820599634658</v>
+        <v>2.192077585139425</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1172,20 +1958,476 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05319322716856423</v>
+        <v>-0.1561382293701452</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1947098184213348</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.8783046616716981</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.872406985743521</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.4142392933463483</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.743727922889454</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.349761951252524</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.841195067520309</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.230843673556283</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.266436652052533</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.716442235462097</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6762635407339082</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.395813286851911</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.555030167800548</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_34.xlsx
+++ b/data/output/evaluasi_34.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
